--- a/COCHE_Papers.xlsx
+++ b/COCHE_Papers.xlsx
@@ -865,55 +865,55 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>42481379</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Ag-Anchored Ti</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>10.1021/acsabm.5c02536</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>ACS applied bio materials</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Bangul Khan, Bilawal Khan, Weibin Zhu, Changqiu Zhou, Ching Yin Fong, Rafi U Shan Ahmad, Iyappan Gunasekran, Mohamed Elhousseini Hilal*, Bee Luan Khoo*</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Bangul Khan, Weibin Zhu, Rafi U Shan Ahmad, Iyappan Gunasekran, Bee Luan Khoo</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>COCHE affiliation</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>COCHE affiliation</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>ITC 2026</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acsabm.5c02536</t>
         </is>

--- a/COCHE_Papers.xlsx
+++ b/COCHE_Papers.xlsx
@@ -759,55 +759,55 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>42696383</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Sample-to-Answer Quantitative Rapid Test for Point-of-Care Monitoring of Urinary Cystatin C Levels.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>10.1021/acssensors.6c02077</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>ACS sensors</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Lok Tim Pang, Miu Ling Lam, Cheuk Chun Szeto, Ting-Hsuan Chen*</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Ting-Hsuan Chen</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>COCHE affiliation</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>COCHE affiliation</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>ITC 2026</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/acssensors.6c02077</t>
         </is>

--- a/COCHE_Papers.xlsx
+++ b/COCHE_Papers.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2926,7 +2926,7 @@
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
@@ -2961,7 +2961,7 @@
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
       <c r="D50" s="3" t="inlineStr"/>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3152,7 +3152,7 @@
       <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr"/>
@@ -6502,7 +6502,7 @@
       <c r="D114" s="3" t="inlineStr"/>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr"/>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr"/>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr"/>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
@@ -6838,7 +6838,7 @@
       <c r="D122" s="3" t="inlineStr"/>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr"/>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr"/>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr"/>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr"/>
@@ -7045,7 +7045,7 @@
       <c r="D127" s="3" t="inlineStr"/>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr"/>
@@ -7080,7 +7080,7 @@
       <c r="D128" s="3" t="inlineStr"/>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr"/>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr"/>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr"/>
@@ -7201,7 +7201,7 @@
       <c r="D131" s="3" t="inlineStr"/>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr"/>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr"/>
@@ -7322,7 +7322,7 @@
       <c r="D134" s="3" t="inlineStr"/>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr"/>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr"/>
@@ -7443,7 +7443,7 @@
       <c r="D137" s="3" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr"/>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr"/>
@@ -7564,7 +7564,7 @@
       <c r="D140" s="3" t="inlineStr"/>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr"/>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr"/>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr"/>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr"/>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr"/>
@@ -12198,7 +12198,7 @@
       <c r="D226" s="3" t="inlineStr"/>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr"/>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr"/>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr"/>
@@ -12362,7 +12362,7 @@
       <c r="D230" s="3" t="inlineStr"/>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr"/>
@@ -12397,7 +12397,7 @@
       <c r="D231" s="3" t="inlineStr"/>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr"/>
@@ -12432,7 +12432,7 @@
       <c r="D232" s="3" t="inlineStr"/>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr"/>
@@ -12510,7 +12510,7 @@
       <c r="D234" s="3" t="inlineStr"/>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr"/>
@@ -12545,7 +12545,7 @@
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr"/>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr"/>
@@ -12666,7 +12666,7 @@
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr"/>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr"/>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr"/>
@@ -12787,7 +12787,7 @@
       <c r="D241" s="3" t="inlineStr"/>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr"/>
@@ -12822,7 +12822,7 @@
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr"/>
@@ -12857,7 +12857,7 @@
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr"/>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr"/>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr"/>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr"/>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr"/>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr"/>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr"/>
@@ -13193,7 +13193,7 @@
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr"/>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr"/>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr"/>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr"/>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr"/>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr"/>
@@ -13486,7 +13486,7 @@
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr"/>
@@ -13525,7 +13525,7 @@
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr"/>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="E327" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F327" s="3" t="inlineStr"/>
@@ -17272,7 +17272,7 @@
       <c r="D328" s="3" t="inlineStr"/>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="E329" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F329" s="3" t="inlineStr"/>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -17397,7 +17397,7 @@
       </c>
       <c r="E331" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F331" s="3" t="inlineStr"/>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="E333" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F333" s="3" t="inlineStr"/>
@@ -17526,7 +17526,7 @@
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="E335" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F335" s="3" t="inlineStr"/>
@@ -17608,7 +17608,7 @@
       <c r="D336" s="3" t="inlineStr"/>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -17643,7 +17643,7 @@
       <c r="D337" s="3" t="inlineStr"/>
       <c r="E337" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F337" s="3" t="inlineStr"/>
@@ -17678,7 +17678,7 @@
       <c r="D338" s="3" t="inlineStr"/>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F339" s="3" t="inlineStr"/>
@@ -17756,7 +17756,7 @@
       <c r="D340" s="3" t="inlineStr"/>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -17795,7 +17795,7 @@
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F341" s="3" t="inlineStr"/>
@@ -17834,7 +17834,7 @@
       <c r="D342" s="3" t="inlineStr"/>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F343" s="3" t="inlineStr"/>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -17955,7 +17955,7 @@
       <c r="D345" s="3" t="inlineStr"/>
       <c r="E345" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F345" s="3" t="inlineStr"/>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F347" s="3" t="inlineStr"/>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="E349" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F349" s="3" t="inlineStr"/>
@@ -18166,7 +18166,7 @@
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F351" s="3" t="inlineStr"/>
@@ -18248,7 +18248,7 @@
       <c r="D352" s="3" t="inlineStr"/>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F353" s="3" t="inlineStr"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -18369,7 +18369,7 @@
       <c r="D355" s="3" t="inlineStr"/>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F355" s="3" t="inlineStr"/>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="E357" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F357" s="3" t="inlineStr"/>
@@ -18494,7 +18494,7 @@
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F359" s="3" t="inlineStr"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="E361" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F361" s="3" t="inlineStr"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="E399" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F399" s="3" t="inlineStr"/>
@@ -20736,7 +20736,7 @@
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="E401" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F401" s="3" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr"/>
@@ -20865,7 +20865,7 @@
       </c>
       <c r="E403" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F403" s="3" t="inlineStr"/>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr"/>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="E405" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F405" s="3" t="inlineStr"/>
@@ -20994,7 +20994,7 @@
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="E407" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F407" s="3" t="inlineStr"/>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr"/>
@@ -21123,7 +21123,7 @@
       </c>
       <c r="E409" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F409" s="3" t="inlineStr"/>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr"/>
@@ -21209,7 +21209,7 @@
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F411" s="3" t="inlineStr"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F413" s="3" t="inlineStr">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="E417" s="3" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="F417" s="3" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="E427" s="3" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="F427" s="3" t="inlineStr">
@@ -22210,7 +22210,7 @@
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="E431" s="3" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="F431" s="3" t="inlineStr">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="E433" s="3" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F433" s="3" t="inlineStr"/>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="E435" s="3" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F435" s="3" t="inlineStr"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr">
@@ -22535,7 +22535,7 @@
       <c r="D437" s="3" t="inlineStr"/>
       <c r="E437" s="3" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F437" s="3" t="inlineStr"/>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="E439" s="3" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="F439" s="3" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>2015-07-01</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr">
@@ -22727,7 +22727,7 @@
       <c r="D441" s="3" t="inlineStr"/>
       <c r="E441" s="3" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F441" s="3" t="inlineStr">
@@ -22774,7 +22774,7 @@
       <c r="D442" s="3" t="inlineStr"/>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="E443" s="3" t="inlineStr">
         <is>
-          <t>2012-10-01</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="F443" s="3" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>2010-06-01</t>
+          <t>2010-06</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="E445" s="3" t="inlineStr">
         <is>
-          <t>2010-03-01</t>
+          <t>2010-03</t>
         </is>
       </c>
       <c r="F445" s="3" t="inlineStr">
@@ -22974,7 +22974,7 @@
       <c r="D446" s="3" t="inlineStr"/>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr">
@@ -23021,7 +23021,7 @@
       <c r="D447" s="3" t="inlineStr"/>
       <c r="E447" s="3" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F447" s="3" t="inlineStr">
@@ -23068,7 +23068,7 @@
       <c r="D448" s="3" t="inlineStr"/>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr">
@@ -23115,7 +23115,7 @@
       <c r="D449" s="3" t="inlineStr"/>
       <c r="E449" s="3" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="F449" s="3" t="inlineStr">
@@ -23162,7 +23162,7 @@
       <c r="D450" s="3" t="inlineStr"/>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr">
@@ -23209,7 +23209,7 @@
       <c r="D451" s="3" t="inlineStr"/>
       <c r="E451" s="3" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="F451" s="3" t="inlineStr">
@@ -23256,7 +23256,7 @@
       <c r="D452" s="3" t="inlineStr"/>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>2005-10-01</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr">
@@ -23303,7 +23303,7 @@
       <c r="D453" s="3" t="inlineStr"/>
       <c r="E453" s="3" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="F453" s="3" t="inlineStr">
@@ -23350,7 +23350,7 @@
       <c r="D454" s="3" t="inlineStr"/>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>2005-07-01</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr">
@@ -23397,7 +23397,7 @@
       <c r="D455" s="3" t="inlineStr"/>
       <c r="E455" s="3" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="F455" s="3" t="inlineStr">
@@ -23444,7 +23444,7 @@
       <c r="D456" s="3" t="inlineStr"/>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr">
@@ -23491,7 +23491,7 @@
       <c r="D457" s="3" t="inlineStr"/>
       <c r="E457" s="3" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="F457" s="3" t="inlineStr">
@@ -23538,7 +23538,7 @@
       <c r="D458" s="3" t="inlineStr"/>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr">
@@ -23585,7 +23585,7 @@
       <c r="D459" s="3" t="inlineStr"/>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F459" s="3" t="inlineStr">
@@ -23632,7 +23632,7 @@
       <c r="D460" s="3" t="inlineStr"/>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="E461" s="3" t="inlineStr">
         <is>
-          <t>-01-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F461" s="3" t="inlineStr"/>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>-01-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="E463" s="3" t="inlineStr">
         <is>
-          <t>-01-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F463" s="3" t="inlineStr"/>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>-01-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr"/>
@@ -23847,7 +23847,7 @@
       <c r="D465" s="3" t="inlineStr"/>
       <c r="E465" s="3" t="inlineStr">
         <is>
-          <t>-01-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F465" s="3" t="inlineStr"/>
